--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104470_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104470_W2.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1916</v>
+        <v>4.4838</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0423</v>
+        <v>3.1485</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1493</v>
+        <v>1.3352</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2244</v>
+        <v>3.224</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8298</v>
+        <v>-0.8246</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0542</v>
+        <v>4.0485</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9548</v>
+        <v>1.9297</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1744</v>
+        <v>-1.1828</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2697</v>
+        <v>1.2942</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1921</v>
+        <v>0.489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3266</v>
+        <v>-0.1862</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5187</v>
+        <v>0.6752</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8706</v>
+        <v>4.1322</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6405</v>
+        <v>2.0539</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2301</v>
+        <v>2.0783</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7039</v>
+        <v>2.7083</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2254</v>
+        <v>-0.2078</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9293</v>
+        <v>2.9161</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8891</v>
+        <v>2.8627</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7506</v>
+        <v>2.7249</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1852</v>
+        <v>-0.1544</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.3556</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1825</v>
+        <v>-0.7389</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2811</v>
+        <v>1.0945</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0196</v>
+        <v>0.3443</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4581</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4385</v>
+        <v>1.3316</v>
       </c>
       <c r="G4" t="n">
-        <v>1.294</v>
+        <v>1.3222</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2467</v>
+        <v>1.0333</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5407</v>
+        <v>0.2889</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0074</v>
+        <v>1.8911</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1172</v>
+        <v>1.2066</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8902</v>
+        <v>0.6845</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2866</v>
+        <v>-0.5689</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3639</v>
+        <v>-0.1733</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6505</v>
+        <v>-0.3956</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3895</v>
+        <v>0.0024</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8135</v>
+        <v>-0.7599</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2031</v>
+        <v>0.7623</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7032</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4822</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2898</v>
+        <v>-0.0635</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5889</v>
+        <v>-0.295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2991</v>
+        <v>0.2315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4491</v>
+        <v>1.2937</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1933</v>
+        <v>-0.2497</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6424</v>
+        <v>1.5434</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4726</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0275</v>
+        <v>0.0959</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4451</v>
+        <v>0.8783</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0236</v>
+        <v>0.3194</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2209</v>
+        <v>-0.3457</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1973</v>
+        <v>0.665</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3953</v>
+        <v>0.3485</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2994</v>
+        <v>-0.6044</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0959</v>
+        <v>0.9529</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.7057</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3462</v>
+        <v>-0.437</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5162</v>
+        <v>-0.8413</v>
       </c>
       <c r="F6" t="n">
-        <v>1.17</v>
+        <v>0.4043</v>
       </c>
       <c r="G6" t="n">
-        <v>1.312</v>
+        <v>0.4468</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0214</v>
+        <v>-0.1952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2905</v>
+        <v>0.642</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9131</v>
+        <v>0.4597</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2122</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7009</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6011</v>
+        <v>-0.0129</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1908</v>
+        <v>-0.2157</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4104</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6847</v>
+        <v>0.2543</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3217</v>
+        <v>0.0648</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6369</v>
+        <v>0.1895</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0771</v>
+        <v>-1.627</v>
       </c>
       <c r="E7" t="n">
-        <v>1.234</v>
+        <v>-2.2081</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.311</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5073</v>
+        <v>-2.1474</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7071</v>
+        <v>0.1407</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1999</v>
+        <v>-2.2881</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6563</v>
+        <v>-1.6479</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>-2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.149</v>
+        <v>-0.4995</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1255</v>
+        <v>-0.4314</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0812</v>
+        <v>-0.3414</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5777</v>
+        <v>-0.6692</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5036</v>
+        <v>0.3278</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8924</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8924</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1148</v>
+        <v>-1.695</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4828</v>
+        <v>0.7533</v>
       </c>
       <c r="F8" t="n">
-        <v>0.368</v>
+        <v>-2.4483</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1471</v>
+        <v>0.5046</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.287</v>
+        <v>-0.1965</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6281</v>
+        <v>0.6465</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.2098</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5189</v>
+        <v>-0.1419</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4417</v>
+        <v>0.129</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0772</v>
+        <v>-0.271</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8335</v>
+        <v>0.4542</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9739</v>
+        <v>0.1067</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1403</v>
+        <v>0.3474</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-2.8814</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3062</v>
+        <v>-3.4748</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4207</v>
+        <v>-1.5452</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8855</v>
+        <v>-1.9296</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5559</v>
+        <v>-2.5479</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7243</v>
+        <v>-1.726</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8316</v>
+        <v>-0.8218</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3542</v>
+        <v>-1.3614</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2017</v>
+        <v>-1.1865</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3424</v>
+        <v>0.1626</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0571</v>
+        <v>-4.8084</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5722</v>
+        <v>-2.4637</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.485</v>
+        <v>-2.3447</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8673</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7143</v>
+        <v>-0.7088</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2012</v>
+        <v>0.2007</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0685</v>
+        <v>-1.059</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2825</v>
+        <v>-0.0395</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1065</v>
+        <v>-6.068</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9346</v>
+        <v>-4.9079</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1719</v>
+        <v>-1.1602</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3724</v>
+        <v>-2.3729</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1861</v>
+        <v>1.1889</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.5585</v>
+        <v>-3.5618</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4409</v>
+        <v>-1.4738</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7073</v>
+        <v>1.6925</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1481</v>
+        <v>-3.1662</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9316</v>
+        <v>-0.8992</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3451</v>
+        <v>0.4054</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4657</v>
+        <v>-0.3743</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8108</v>
+        <v>0.7798</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7355</v>
+        <v>1.7205</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.2551</v>
+        <v>-9.2134</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.056699999999999</v>
+        <v>-7.292899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.198399999999999</v>
+        <v>-1.920800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.548000000000001</v>
+        <v>1.573</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3178999999999998</v>
+        <v>-0.2887999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.865799999999999</v>
+        <v>1.8619</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6713</v>
+        <v>4.4816</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7403</v>
+        <v>1.6562</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9313</v>
+        <v>2.825600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1233</v>
+        <v>-2.9087</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0582</v>
+        <v>-1.945</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0654</v>
+        <v>-0.9639</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R12" t="n">
-        <v>6.805000000000001</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0435</v>
+        <v>2.0911</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.3247</v>
+        <v>-3.2779</v>
       </c>
       <c r="U12" t="n">
-        <v>5.3683</v>
+        <v>5.368999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.0416</v>
+        <v>-6.0486</v>
       </c>
       <c r="W12" t="n">
-        <v>5.2066</v>
+        <v>5.1616</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.2481</v>
+        <v>-11.2102</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.512</v>
+        <v>6.9306</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1112</v>
+        <v>4.431</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4008</v>
+        <v>2.4996</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3908</v>
+        <v>2.3985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1357</v>
+        <v>0.1323</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2551</v>
+        <v>2.2662</v>
       </c>
       <c r="J13" t="n">
-        <v>1.148</v>
+        <v>1.1319</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0835</v>
+        <v>-0.0969</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2428</v>
+        <v>1.2666</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7446</v>
+        <v>-0.3297</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1825</v>
+        <v>-0.8296</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4379</v>
+        <v>0.4999</v>
       </c>
       <c r="V13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5616</v>
+        <v>4.364</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7755</v>
+        <v>2.401</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7861</v>
+        <v>1.963</v>
       </c>
       <c r="G14" t="n">
-        <v>3.012</v>
+        <v>3.0037</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1702</v>
+        <v>-1.1744</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1822</v>
+        <v>4.1782</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4065</v>
+        <v>2.3849</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3558</v>
+        <v>3.3436</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6055</v>
+        <v>0.6189</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5762</v>
+        <v>0.3798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2072</v>
+        <v>0.3637</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6056</v>
+        <v>3.0529</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1087</v>
+        <v>2.3796</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4969</v>
+        <v>0.6734</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1091</v>
+        <v>1.111</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8423</v>
+        <v>0.8385</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7963</v>
+        <v>1.7816</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6871</v>
+        <v>-0.6706</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0843</v>
+        <v>0.5353</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8075</v>
+        <v>0.1019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2767</v>
+        <v>0.4335</v>
       </c>
       <c r="V15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4793</v>
+        <v>2.1259</v>
       </c>
       <c r="E16" t="n">
-        <v>1.41</v>
+        <v>1.1575</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0693</v>
+        <v>0.9683</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.159</v>
+        <v>-1.1493</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7432</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4158</v>
+        <v>-0.4109</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.24</v>
+        <v>-0.2498</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.8995</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0919</v>
+        <v>-0.2696</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5353</v>
+        <v>-0.7716</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6273</v>
+        <v>0.5021</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2741</v>
+        <v>1.6739</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4697</v>
+        <v>-0.0386</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7439</v>
+        <v>1.7125</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5964</v>
+        <v>-0.6071</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3868</v>
+        <v>1.3817</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9832</v>
+        <v>-1.9889</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1016</v>
+        <v>-0.1381</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0016</v>
+        <v>1.9855</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1033</v>
+        <v>-2.1236</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4948</v>
+        <v>-0.469</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0368</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4608</v>
+        <v>-0.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0.424</v>
+        <v>0.3605</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.096</v>
+        <v>0.734</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5884</v>
+        <v>0.6743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.0597</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4491</v>
+        <v>-0.877</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1746</v>
+        <v>0.1836</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2745</v>
+        <v>-1.0606</v>
       </c>
       <c r="J18" t="n">
-        <v>0.289</v>
+        <v>0.024</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4573</v>
+        <v>0.0689</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7463</v>
+        <v>-0.0449</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7381</v>
+        <v>-0.9011</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2828</v>
+        <v>0.1146</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5056</v>
+        <v>-0.2312</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2994</v>
+        <v>-0.4392</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2061</v>
+        <v>0.208</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8678</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3896</v>
+        <v>0.4507</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5654</v>
+        <v>-1.033</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1759</v>
+        <v>1.4837</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.882</v>
+        <v>0.3565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1789</v>
+        <v>1.2219</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0609</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0292</v>
+        <v>-0.9085</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0693</v>
+        <v>0.6335</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.04</v>
+        <v>-1.542</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9113</v>
+        <v>1.265</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1096</v>
+        <v>0.5884</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0209</v>
+        <v>0.6766</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5677</v>
+        <v>-0.3414</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>-0.6692</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0112</v>
+        <v>0.3278</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1677</v>
+        <v>0.0757</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2291</v>
+        <v>0.1105</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3968</v>
+        <v>-0.0348</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3794</v>
+        <v>-0.4461</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2457</v>
+        <v>-0.1752</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8663</v>
+        <v>-0.271</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8711</v>
+        <v>0.2826</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6643</v>
+        <v>-0.4621</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5354</v>
+        <v>0.7447</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2505</v>
+        <v>-0.7287</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5814</v>
+        <v>0.287</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6691</v>
+        <v>-1.0157</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6388</v>
+        <v>0.4716</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>-0.1721</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2655</v>
+        <v>0.6437</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7071</v>
+        <v>-0.8603</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0324</v>
+        <v>-0.3372</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4163</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3839</v>
+        <v>0.6321</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.786</v>
+        <v>-0.7903</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3248</v>
+        <v>-0.3191</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4612</v>
+        <v>-0.4712</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1279</v>
+        <v>-1.1514</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3419</v>
+        <v>0.3611</v>
       </c>
       <c r="N21" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1272</v>
+        <v>-0.4378</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2925</v>
+        <v>-0.0752</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3013</v>
+        <v>-1.5062</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5324</v>
+        <v>0.2822</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8338</v>
+        <v>-1.7883</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6877</v>
+        <v>-1.6931</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3721</v>
+        <v>0.3568</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2975</v>
+        <v>0.2823</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0599</v>
+        <v>-2.0499</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0935</v>
+        <v>-0.1105</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0668</v>
+        <v>-0.0359</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6239</v>
+        <v>-1.5191</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4897</v>
+        <v>-2.1666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8659</v>
+        <v>0.6475</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.331</v>
+        <v>-0.3325</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3723</v>
+        <v>1.3701</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7033</v>
+        <v>-1.7026</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9611</v>
+        <v>0.9394</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9784</v>
+        <v>-0.9912</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2921</v>
+        <v>-1.2719</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0641</v>
+        <v>0.0395</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-0.8296</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1184</v>
+        <v>0.8691</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8732</v>
+        <v>-5.7863</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2884</v>
+        <v>-5.3078</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5848</v>
+        <v>-0.4785</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.548</v>
+        <v>-2.5473</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2712</v>
+        <v>-1.2723</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2768</v>
+        <v>-1.275</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0099</v>
+        <v>-1.0025</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2156</v>
+        <v>-0.122</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1322</v>
+        <v>0.2265</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.2551</v>
+        <v>10.2589</v>
       </c>
       <c r="E25" t="n">
-        <v>2.198400000000001</v>
+        <v>1.920799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>8.056700000000001</v>
+        <v>8.338200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.5479</v>
+        <v>-1.573000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3181</v>
+        <v>0.2887000000000004</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8659</v>
+        <v>-1.8618</v>
       </c>
       <c r="J25" t="n">
-        <v>3.123500000000001</v>
+        <v>2.9086</v>
       </c>
       <c r="K25" t="n">
-        <v>2.0581</v>
+        <v>1.9447</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0652</v>
+        <v>0.9636999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.6714</v>
+        <v>-4.4816</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7401</v>
+        <v>-1.656</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.9313</v>
+        <v>-2.8256</v>
       </c>
       <c r="P25" t="n">
-        <v>6.805100000000001</v>
+        <v>6.8291</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0433</v>
+        <v>-1.0455</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.368200000000001</v>
+        <v>-5.3691</v>
       </c>
       <c r="U25" t="n">
-        <v>4.3248</v>
+        <v>4.3237</v>
       </c>
       <c r="V25" t="n">
-        <v>6.0415</v>
+        <v>6.048500000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>11.2481</v>
+        <v>11.2102</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.206600000000001</v>
+        <v>-5.1617</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104470_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104470_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-11.2102</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104470_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.1617</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
